--- a/outputs/recomendaciones_tfidf_explicadas.xlsx
+++ b/outputs/recomendaciones_tfidf_explicadas.xlsx
@@ -489,40 +489,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0348</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y</t>
+          <t>Propiedad intelectual</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.14318</v>
+        <v>0.147837</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_valencia/txt/22548_propiedad_intelectual.txt</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ebc; ris3 cv; ris3; tecnológica; cv; trl; conocimiento; base; investigación; tecnología; científicos; de conocimiento</t>
+          <t>propiedad intelectual; intelectual; propiedad; activos; empresa; innovación; para; con</t>
         </is>
       </c>
     </row>
@@ -542,40 +542,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>doc_0088</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22548_propiedad_intelectual</t>
+          <t>EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.118101</v>
+        <v>0.143228</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/22548_propiedad_intelectual.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>propiedad intelectual; intelectual; propiedad; activos; empresa; innovación; para; con</t>
+          <t>ebc; ris3 cv; ris3; tecnológica; cv; trl; conocimiento; base; investigación; tecnología; científicos; de conocimiento</t>
         </is>
       </c>
     </row>
@@ -595,40 +595,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0270</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Propiedad industrial e intelectual (28)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.097577</v>
+        <v>0.10233</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_valencia/txt/1103_propiedad_industrial_e_intelectual_28.txt</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>transferencia; innovación; tecnológica; empresa; la innovación; transferencia tecnológica; fase; base; de base; para; de la; empresarial</t>
+          <t>intelectual; propiedad; innovación; la innovación; manuales; de la; empresarial; manuales de; gestión empresarial; gestión</t>
         </is>
       </c>
     </row>
@@ -648,40 +648,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>doc_0010</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1103_propiedad_industrial_e_intelectual_28</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.091019</v>
+        <v>0.097568</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/1103_propiedad_industrial_e_intelectual_28.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>intelectual; propiedad; innovación; la innovación; manuales; de la; empresarial; manuales de; gestión empresarial; gestión</t>
+          <t>transferencia; innovación; tecnológica; empresa; la innovación; transferencia tecnológica; fase; base; de base; para; de la; empresarial</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>doc_0334</t>
+          <t>doc_0201</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.084353</v>
+        <v>0.084345</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe COTEC 2014.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe COTEC 2014.pdf</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -778,11 +778,11 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.07895199999999999</v>
+        <v>0.078976</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.078559</v>
+        <v>0.078434</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>doc_0348</t>
+          <t>doc_0215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -884,11 +884,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.072602</v>
+        <v>0.07262</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22691_manual_diagrama_integral_de_startups</t>
+          <t>Manual Diagrama integral de startups</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.072294</v>
+        <v>0.072255</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>doc_0149</t>
+          <t>doc_0016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -990,11 +990,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.07074900000000001</v>
+        <v>0.070767</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Mejoras en las deducciones fiscales por IDiGuía.pdf</t>
+          <t>data/raw/ceei_elche/original/Mejoras en las deducciones fiscales por IDiGuía.pdf</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.228107</v>
+        <v>0.230606</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>doc_0401</t>
+          <t>doc_0280</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22691_manual_diagrama_integral_de_startups</t>
+          <t>Lean Startup para el Escalado de Startups</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1087,25 +1087,25 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.116688</v>
+        <v>0.12437</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/22691_manual_diagrama_integral_de_startups.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14625_lean_startup_para_el_escalado_de_startups.txt</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>escalado; estrategia; startup; kpis; market; tracción; métricas; fase; validado; procesos; capital; market fit</t>
+          <t>escalado; startup; escalado de; de startups; startups; producto</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>doc_0020</t>
+          <t>doc_0401</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14625_lean_startup_para_el_escalado_de_startups</t>
+          <t>Manual Diagrama integral de startups</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1140,25 +1140,25 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.105161</v>
+        <v>0.117059</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14625_lean_startup_para_el_escalado_de_startups.txt</t>
+          <t>documentos_ceei_valencia/22691_manual_diagrama_integral_de_startups.pdf</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>startup; escalado; escalado de; de startups; startups; producto</t>
+          <t>escalado; estrategia; startup; kpis; market; tracción; métricas; fase; validado; procesos; capital; market fit</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22544_alianzas_estrategicas_entre_empresas_y_startups_como_construir_relaciones_que_beneficien_a</t>
+          <t>Alianzas estratégicas entre empresas y startups Cómo construir relaciones que beneficien a ambas partes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.101206</v>
+        <v>0.099033</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.09854400000000001</v>
+        <v>0.09854300000000001</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>doc_0332</t>
+          <t>doc_0199</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1308,11 +1308,11 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.07985200000000001</v>
+        <v>0.07985299999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.074355</v>
+        <v>0.07435799999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>doc_0186</t>
+          <t>doc_0053</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1414,11 +1414,11 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.072785</v>
+        <v>0.07277699999999999</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Internacionalización.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Consultoría de Internacionalización.pdf</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23069_plan_de_innovacion</t>
+          <t>Plan de innovación</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.067258</v>
+        <v>0.066953</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>doc_0304</t>
+          <t>doc_0171</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/KPIs_ Indicadores Clave de RendimientoINFOGRAFÍAS.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/KPIs_ Indicadores Clave de RendimientoINFOGRAFÍAS.pdf</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>doc_0340</t>
+          <t>doc_0207</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro de AESEC_Esta acción ha sido desarrollada en colabo.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro de AESEC_Esta acción ha sido desarrollada en colabo.pdf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1602,22 +1602,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>doc_0365</t>
+          <t>doc_0337</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Despacho Profesional_ Servicios de Consultoría</t>
+          <t>Despacho Profesional: Servicios de Consultoría Modelo de Negocio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Modelos_de_Negocio_texto</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.09307699999999999</v>
+        <v>0.097848</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Despacho Profesional_ Servicios de Consultoría.txt</t>
+          <t>data/raw/ceei_valencia/txt/21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio.txt</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>de consultoría; consultoría; servicios; profesional; servicios de; de servicios; de mercado; para; definir; mercado; modelo; del</t>
+          <t>de consultoría; consultoría; profesional; servicios; de negocio; negocio; servicios de; modelo; modelo de; modelos de; modelos; de servicios</t>
         </is>
       </c>
     </row>
@@ -1655,22 +1655,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>doc_0077</t>
+          <t>doc_0232</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio</t>
+          <t>Despacho Profesional: Servicios de Consultoría</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Modelos_de_Negocio_texto</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.08467</v>
+        <v>0.092806</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Despacho Profesional_ Servicios de Consultoría.txt</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>de consultoría; consultoría; profesional; servicios; de negocio; negocio; servicios de; modelo; modelos de; modelos; modelo de; de servicios</t>
+          <t>de consultoría; consultoría; profesional; servicios; servicios de; de servicios; de mercado; para; definir; mercado; modelo; del</t>
         </is>
       </c>
     </row>
@@ -1708,40 +1708,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>doc_0339</t>
+          <t>doc_0285</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol</t>
+          <t>Servicios profesionales empresariales Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.07721699999999999</v>
+        <v>0.087503</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>silver; del; servicios; para; baja; negocio; de negocio; modelos; modelos de; economía; crear; nicho</t>
+          <t>servicios profesionales; consultoría; servicios; profesionales; negocio de; de negocio; buscar; negocio; modelo de; para; modelo; guías de</t>
         </is>
       </c>
     </row>
@@ -1761,40 +1761,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>doc_0025</t>
+          <t>doc_0206</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.07607999999999999</v>
+        <v>0.077219</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol.pdf</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>servicios profesionales; consultoría; servicios; buscar; profesionales; de negocio; negocio de; negocio; para; modelo de; modelo; guías de</t>
+          <t>silver; del; servicios; para; baja; negocio; de negocio; modelos; modelos de; economía; crear; nicho</t>
         </is>
       </c>
     </row>
@@ -1814,40 +1814,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0311</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Guía de Digitalización para Pymes Manual de Gestión Empresarial elaborado por Leonard Pera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.07066600000000001</v>
+        <v>0.07332900000000001</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_valencia/txt/18339_guía_de_digitalización_para_pymes_manual_de_gestión_empresarial_elaborado_por_leonard_pera.txt</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>red; red de; empresarial; para; servicios; consultoría; del; de negocio; negocio; con; economía; asesoramiento</t>
+          <t>digitalización para; digitalización; de digitalización; empresarial; para; tecnología de; red; especializados; recursos; tecnología; manuales; con</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>doc_0188</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Consultoría de Proyectos y Captación de Financiación</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1891,16 +1891,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.07052799999999999</v>
+        <v>0.070669</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Proyectos y Captación de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>consultoría; de consultoría; de contactos; servicios; contactos; consultora; profesionales; empresarial; para; profesionales especializados; del; un</t>
+          <t>red; red de; empresarial; para; servicios; consultoría; del; de negocio; negocio; con; economía; asesoramiento</t>
         </is>
       </c>
     </row>
@@ -1920,22 +1920,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>doc_0394</t>
+          <t>doc_0055</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio</t>
+          <t>Consultoría de Proyectos y Captación de Financiación</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.068131</v>
+        <v>0.07052799999999999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Consultoría de Proyectos y Captación de Financiación.pdf</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>mentoría; red de; de mentoría; crear una; red; para; de contactos; tecnología; contactos; buscar; supervivencia; crear</t>
+          <t>consultoría; de consultoría; de contactos; servicios; contactos; consultora; profesionales; empresarial; para; profesionales especializados; del; un</t>
         </is>
       </c>
     </row>
@@ -1973,40 +1973,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>doc_0337</t>
+          <t>doc_0355</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_</t>
+          <t>Consultoría en gestión del agua y reciclaje Modelo de Negocio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.067078</v>
+        <v>0.068685</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
+          <t>data/raw/ceei_valencia/txt/23078_consultoría_en_gestión_del_agua_y_reciclaje_modelo_de_negocio.txt</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>silver; servicios; del; red; red de; para; economía; de servicios; empresarial; con; tecnología; silver en</t>
+          <t>consultoría; de negocio; de consultoría; negocio; red; digitalización; del; modelo; modelo de; modelos de; modelos; asesoramiento</t>
         </is>
       </c>
     </row>
@@ -2026,22 +2026,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>doc_0186</t>
+          <t>doc_0394</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Consultoría de Internacionalización</t>
+          <t>Networking, mentoring y techscouting Tres modelos de innovación abierta para tu negocio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.066608</v>
+        <v>0.06843200000000001</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Internacionalización.pdf</t>
+          <t>documentos_ceei_valencia/20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio.pdf</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>consultoría; servicios; contactos; de consultoría; consultora; red de; consolidada; consolidada en; una consultora; profesionales; asesoramiento; red</t>
+          <t>mentoría; red de; de mentoría; para; crear una; red; de contactos; tecnología; contactos; modelos; buscar; supervivencia</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>doc_0348</t>
+          <t>doc_0215</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.09193999999999999</v>
+        <v>0.09194099999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio</t>
+          <t>Networking, mentoring y techscouting Tres modelos de innovación abierta para tu negocio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.074974</v>
+        <v>0.07438699999999999</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>mentoría; de mentoría; conocimiento; para; formalizar; mentor; buscar; redes; con; profesionales; profesional; su</t>
+          <t>mentoría; de mentoría; conocimiento; para; formalizar; mentor; buscar; redes; con; profesionales; profesional; modelos</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>doc_0414</t>
+          <t>doc_0285</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23032_servicios_de_fotografia_y_video_para_empresas</t>
+          <t>Servicios profesionales empresariales Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2200,25 +2200,25 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.069517</v>
+        <v>0.071546</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/23032_servicios_de_fotografia_y_video_para_empresas.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>servicios; profesionales; profesional; empresarial; para; redes; asesoramiento; del; servicios de; profesional con; en servicios; estabilidad</t>
+          <t>servicios profesionales; profesionales; servicios; buscar; negocios; de negocios; para; gestión; guías de; empresas; ventaja; documentación</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>doc_0254</t>
+          <t>doc_0414</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2262,11 +2262,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.069206</v>
+        <v>0.06922200000000001</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Servicios de Fotografía y Vídeo para Empresas.pdf</t>
+          <t>documentos_ceei_valencia/23032_servicios_de_fotografia_y_video_para_empresas.pdf</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2291,40 +2291,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>doc_0025</t>
+          <t>doc_0121</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Servicios de Fotografía y Vídeo para Empresas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.06331000000000001</v>
+        <v>0.069207</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Servicios de Fotografía y Vídeo para Empresas.pdf</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>servicios profesionales; profesionales; servicios; buscar; negocios; de negocios; para; gestión; guías de; empresas; documentación; ventaja</t>
+          <t>servicios; profesionales; profesional; empresarial; para; redes; asesoramiento; del; servicios de; profesional con; en servicios; estabilidad</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2368,11 +2368,11 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.062062</v>
+        <v>0.062067</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2421,11 +2421,11 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.060664</v>
+        <v>0.060666</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>doc_0192</t>
+          <t>doc_0059</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2474,11 +2474,11 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.059662</v>
+        <v>0.059664</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Despachos Profesionales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Despachos Profesionales.pdf</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23019_centro_especializado_en_vehiculos_electricos</t>
+          <t>Centro especializado en vehículos eléctricos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.058917</v>
+        <v>0.05887</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>doc_0349</t>
+          <t>doc_0216</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2580,11 +2580,11 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.058872</v>
+        <v>0.058869</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio/Centro especializado en vehículos eléctricos.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio/Centro especializado en vehículos eléctricos.pdf</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>doc_0323</t>
+          <t>doc_0190</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2633,11 +2633,11 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.282578</v>
+        <v>0.282572</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>doc_0337</t>
+          <t>doc_0204</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2686,11 +2686,11 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.138386</v>
+        <v>0.138382</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>doc_0346</t>
+          <t>doc_0213</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2739,11 +2739,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.121609</v>
+        <v>0.121612</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resultados fase entender HUB Innovación Colaborativa Territorial 2023- Nueva Ruralidad Regenerativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resultados fase entender HUB Innovación Colaborativa Territorial 2023- Nueva Ruralidad Regenerativa.pdf</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>doc_0369</t>
+          <t>doc_0236</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2792,11 +2792,11 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.113158</v>
+        <v>0.113152</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Economía Circular.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Economía Circular.txt</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>doc_0272</t>
+          <t>doc_0139</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2845,11 +2845,11 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.109779</v>
+        <v>0.10977</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Turismo Rural.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Turismo Rural.pdf</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>doc_0032</t>
+          <t>doc_0292</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14822_economía_circular_modelo_de_negocio</t>
+          <t>Economía Circular Modelo de Negocio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.095191</v>
+        <v>0.109733</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>doc_0347</t>
+          <t>doc_0214</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2951,11 +2951,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.088564</v>
+        <v>0.088565</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resultados proyecto piloto HUB Innovación Colaborativa Territorial 2021 - 2022.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resultados proyecto piloto HUB Innovación Colaborativa Territorial 2021 - 2022.pdf</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.084052</v>
+        <v>0.08405899999999999</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>doc_0330</t>
+          <t>doc_0197</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe 2023_ Ecosistema local energético colaborativo_ autosuficiente_ eficiente y sostenible en Salinas_Resultados de .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe 2023_ Ecosistema local energético colaborativo_ autosuficiente_ eficiente y sostenible en Salinas_Resultados de .pdf</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>doc_0211</t>
+          <t>doc_0078</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Empresas de Servicios Sociales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Empresas de Servicios Sociales.pdf</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>doc_0135</t>
+          <t>doc_0002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.189507</v>
+        <v>0.189503</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guia de responsabilidad social de la empresaGuía d.pdf</t>
+          <t>data/raw/ceei_elche/original/Guia de responsabilidad social de la empresaGuía d.pdf</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>22980_sostenibilidad_decidir_hoy_para_no_limitar_el_crecimiento_manana</t>
+          <t>Sostenibilidad: decidir hoy para no limitar el crecimiento mañana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.127742</v>
+        <v>0.127551</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>doc_0147</t>
+          <t>doc_0014</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3269,11 +3269,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.104516</v>
+        <v>0.104518</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Trámites de constitución de empresa.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Trámites de constitución de empresa.pdf</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>doc_0372</t>
+          <t>doc_0239</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3322,11 +3322,11 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.08568199999999999</v>
+        <v>0.08612300000000001</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Empresa de Tiempo Libre.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Empresa de Tiempo Libre.txt</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>doc_0084</t>
+          <t>doc_0344</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22448_empresa_de_tiempo_libre_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Empresa de Tiempo Libre Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.080846</v>
+        <v>0.076793</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>doc_0211</t>
+          <t>doc_0078</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Empresas de Servicios Sociales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Empresas de Servicios Sociales.pdf</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>doc_0040</t>
+          <t>doc_0245</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18162_la_sostenibilidad_en_la_empresa._aplicación_práctica_a_las_pymes_61_manual_elaborado_por_joan_ramon_sanchis_palacio_vane</t>
+          <t>Gestión Cultural</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Modelos_de_Negocio_texto</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.07285700000000001</v>
+        <v>0.072198</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/18162_la_sostenibilidad_en_la_empresa._aplicación_práctica_a_las_pymes_61_manual_elaborado_por_joan_ramon_sanchis_palacio_vane.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Gestión Cultural.txt</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>social; responsabilidad social; ods; responsabilidad; alinear; empresarial; con; del; para</t>
+          <t>social; impacto social; impacto; sociales; con</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>doc_0378</t>
+          <t>doc_0340</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Modelos_de_Negocio_texto</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3534,16 +3534,16 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.072198</v>
+        <v>0.067505</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Gestión Cultural.txt</t>
+          <t>data/raw/ceei_valencia/txt/22444_gestión_cultural.txt</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>social; impacto social; impacto; sociales; con</t>
+          <t>social; impacto social; impacto; sociales; modelos; con</t>
         </is>
       </c>
     </row>
@@ -3563,40 +3563,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>doc_0080</t>
+          <t>doc_0175</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22444_gestión_cultural</t>
+          <t>Pasos para realizar el Plan Social Media de tu negocio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Infografias</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.06911</v>
+        <v>0.06705899999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/22444_gestión_cultural.txt</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Pasos para realizar el Plan Social Media de tu negocio.pdf</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>social; impacto social; impacto; sociales; modelos; con</t>
+          <t>social; plan; sociales; media; para</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>doc_0308</t>
+          <t>doc_0200</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pasos para realizar el Plan Social Media de tu negocio</t>
+          <t>Informe Benchmarking CEEI Elche 2020_ Impacto COVID19_ Claves para la Recuperación Económica 2021Informes y estudios</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Infografias</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.067055</v>
+        <v>0.06475400000000001</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Pasos para realizar el Plan Social Media de tu negocio.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2020_ Impacto COVID19_ Claves para la Recuperación Económica 2021Informes y estudios.pdf</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>social; plan; sociales; media; para</t>
+          <t>impacto; economía; social; para; del; sociales; plan; de economía; con; modelos; empresarial; proyecto</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>doc_0123</t>
+          <t>doc_0383</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6891_metodología_lean_startup_41_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Metodología Lean Startup (41) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.145535</v>
+        <v>0.163419</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23022_innovacion_interna_metodologias_agiles_de_innovacion_ii</t>
+          <t>Innovación interna: metodologías ágiles de innovación II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.144804</v>
+        <v>0.144247</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>doc_0020</t>
+          <t>doc_0280</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14625_lean_startup_para_el_escalado_de_startups</t>
+          <t>Lean Startup para el Escalado de Startups</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.124826</v>
+        <v>0.139989</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>doc_0325</t>
+          <t>doc_0192</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3852,11 +3852,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.117068</v>
+        <v>0.117011</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Business Innovation Kit-Bikceei 2020.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Business Innovation Kit-Bikceei 2020.pdf</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>doc_0278</t>
+          <t>doc_0145</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3905,11 +3905,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.106036</v>
+        <v>0.106068</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/3 Nuevas metodologías BIK para empresas y emprendedoresPara emprendedores_ startups y pymes.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/3 Nuevas metodologías BIK para empresas y emprendedoresPara emprendedores_ startups y pymes.pdf</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3934,40 +3934,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>doc_0013</t>
+          <t>doc_0167</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11900_producto_mínimo_viable_51_autor_roberto_touza</t>
+          <t>Gestión Ágil y StartupPara emprendedores y startups</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Infografias</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.093488</v>
+        <v>0.09074400000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/11900_producto_mínimo_viable_51_autor_roberto_touza.txt</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Gestión Ágil y StartupPara emprendedores  y startups.pdf</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>lean startup; lean; startup; metodología lean; metodología; empresarial; un; con</t>
+          <t>startup; lean startup; metodología; lean; de negocio; negocio; inicial; un proyecto; aprender; proyecto; madurez; con</t>
         </is>
       </c>
     </row>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>doc_0300</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gestión Ágil y StartupPara emprendedores y startups</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Infografias</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4011,16 +4011,16 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.090716</v>
+        <v>0.088841</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Gestión Ágil y StartupPara emprendedores  y startups.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>startup; lean startup; metodología; lean; de negocio; negocio; inicial; un proyecto; aprender; proyecto; madurez; con</t>
+          <t>metodología; startup; idea; lean; de negocio; negocio; universidad; lean startup; fase; programas; emprendimiento; modelo</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0199</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.088819</v>
+        <v>0.085817</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>metodología; startup; idea; lean; de negocio; negocio; universidad; lean startup; fase; programas; emprendimiento; modelo</t>
+          <t>startup; programas; idea; emprendimiento; fase; de negocio; lean startup; lean; negocio; un; modelo; programas de</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>doc_0332</t>
+          <t>doc_0211</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios</t>
+          <t>Informe GEM 2018-19 sobre el ecosistema emprendedor en España</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4117,16 +4117,16 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.085816</v>
+        <v>0.083492</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe GEM 2018-19 sobre el ecosistema emprendedor en España.pdf</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>startup; programas; idea; emprendimiento; fase; de negocio; lean startup; lean; negocio; un; modelo; programas de</t>
+          <t>emprendedora; emprendimiento; emprendedoras; en fase; inicial; universidad; fase; negocio; semilla; un; idea; de emprendimiento</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.083527</v>
+        <v>0.083402</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>doc_0311</t>
+          <t>doc_0178</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4223,11 +4223,11 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.07148400000000001</v>
+        <v>0.071424</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Recursos Gratuitos_ Creación y Crecimiento de empresasCerca de 600 recursos para emprendedores_ startups y pymes.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Recursos Gratuitos_ Creación y Crecimiento de empresasCerca de 600 recursos para emprendedores_ startups y pymes.pdf</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4276,11 +4276,11 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.068969</v>
+        <v>0.068967</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>doc_0227</t>
+          <t>doc_0094</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4329,11 +4329,11 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.056072</v>
+        <v>0.056077</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Gestoría Administrativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Gestoría Administrativa.pdf</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>doc_0101</t>
+          <t>doc_0361</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>244_plan_y_presupuesto_de_comunicación_6_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Plan y Presupuesto de Comunicación (6) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.052118</v>
+        <v>0.052879</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>doc_0328</t>
+          <t>doc_0195</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4435,11 +4435,11 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.050671</v>
+        <v>0.050662</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Estudio sobre creación de un Fondo de Garantía para la concesión de microcréditosInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Estudio sobre creación de un Fondo de Garantía para la concesión de microcréditosInformes y estudios.pdf</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4464,40 +4464,40 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>doc_0183</t>
+          <t>doc_0370</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Community Manager</t>
+          <t>Plan de Internacionalización de Empresas (16) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.048768</v>
+        <v>0.050268</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Community Manager.pdf</t>
+          <t>data/raw/ceei_valencia/txt/330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes.txt</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>marketing; digital; marketing digital; de marketing; plan de; plan; planes de; por; media; planes; servicios; para</t>
+          <t>plan; plan de; manuales; marketing; para; manuales de; empresarial; un</t>
         </is>
       </c>
     </row>
@@ -4517,12 +4517,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>doc_0110</t>
+          <t>doc_0312</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Claves para Elaborar un Plan de Igualdad Manual de Gestión Empresarial elaborado por Sandra Merchán</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4541,16 +4541,16 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.045985</v>
+        <v>0.049948</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes.txt</t>
+          <t>data/raw/ceei_valencia/txt/18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán.txt</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>plan; plan de; manuales; marketing; para; manuales de; empresarial; un</t>
+          <t>plan de; plan; un plan; por; laboral; para; planes de; manuales; empresarial; planes; manuales de; un</t>
         </is>
       </c>
     </row>
@@ -4570,40 +4570,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>doc_0052</t>
+          <t>doc_0050</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán</t>
+          <t>Community Manager</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.045263</v>
+        <v>0.04875</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán.txt</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Community Manager.pdf</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>plan de; plan; laboral; por; un plan; planes de; para; manuales; planes; empresarial; manuales de; un</t>
+          <t>marketing; digital; marketing digital; de marketing; plan de; plan; planes de; por; media; planes; servicios; para</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>doc_0323</t>
+          <t>doc_0190</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4647,11 +4647,11 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.045255</v>
+        <v>0.045249</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>doc_0299</t>
+          <t>doc_0166</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Fases Ecosistema Emprendimiento de la Comunitat Valenciana.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Fases Ecosistema Emprendimiento de la Comunitat Valenciana.pdf</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
